--- a/downloads/media.xlsx
+++ b/downloads/media.xlsx
@@ -462,7 +462,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Every image and video file</t>
+          <t>Johnson, Levy and NutraGen websites: every image and video</t>
         </is>
       </c>
     </row>

--- a/downloads/media.xlsx
+++ b/downloads/media.xlsx
@@ -462,7 +462,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Johnson, Levy and NutraGen websites: every image and video</t>
+          <t>Photos and videos from Dr. Johnson's, Dr. Levy's and NutraGen's websites</t>
         </is>
       </c>
     </row>

--- a/downloads/media.xlsx
+++ b/downloads/media.xlsx
@@ -654,7 +654,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -714,7 +714,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2391,7 +2391,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2874,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3198,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3819,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4143,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4899,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5115,7 +5115,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -5978,7 +5978,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6235,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7094,7 +7094,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7378,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7405,7 +7405,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7763,7 +7763,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7824,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8453,7 +8453,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8669,7 +8669,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8723,7 +8723,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8912,7 +8912,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9108,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9169,7 +9169,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9365,7 +9365,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9696,7 +9696,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9777,7 +9777,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9831,7 +9831,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9885,7 +9885,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9912,7 +9912,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9966,7 +9966,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -9993,7 +9993,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10020,7 +10020,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10135,7 +10135,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10189,7 +10189,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10351,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10378,7 +10378,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10405,7 +10405,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10432,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10459,7 +10459,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10486,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10540,7 +10540,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10628,7 +10628,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10709,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10763,7 +10763,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10817,7 +10817,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11033,7 +11033,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11067,7 +11067,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11121,7 +11121,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11229,7 +11229,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11283,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11310,7 +11310,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11445,7 +11445,7 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11553,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11580,7 +11580,7 @@
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11607,7 +11607,7 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11715,7 +11715,7 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11796,7 +11796,7 @@
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11925,7 +11925,7 @@
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11959,7 +11959,7 @@
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -11993,7 +11993,7 @@
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12095,7 +12095,7 @@
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12210,7 @@
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12264,7 @@
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12291,7 @@
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12399,7 +12399,7 @@
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12426,7 @@
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12534,7 +12534,7 @@
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12561,7 +12561,7 @@
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12588,7 @@
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12615,7 +12615,7 @@
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="E231" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12777,7 +12777,7 @@
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="E233" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12858,7 +12858,7 @@
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12885,7 +12885,7 @@
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12939,7 +12939,7 @@
       </c>
       <c r="E238" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12966,7 +12966,7 @@
       </c>
       <c r="E239" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -12993,7 +12993,7 @@
       </c>
       <c r="E240" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13020,7 +13020,7 @@
       </c>
       <c r="E241" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="E243" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="E245" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="E246" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="E247" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13169,7 +13169,7 @@
       </c>
       <c r="E248" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13196,7 +13196,7 @@
       </c>
       <c r="E249" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13223,7 +13223,7 @@
       </c>
       <c r="E250" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13250,7 +13250,7 @@
       </c>
       <c r="E251" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13496,7 +13496,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13581,7 +13581,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13763,7 +13763,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13817,7 +13817,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13844,7 +13844,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13925,7 +13925,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -13979,7 +13979,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14033,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14060,7 +14060,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14087,7 +14087,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14141,7 +14141,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14168,7 +14168,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14222,7 +14222,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14249,7 +14249,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14330,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14411,7 +14411,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14465,7 +14465,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14492,7 +14492,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14519,7 +14519,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14546,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14573,7 +14573,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14600,7 +14600,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14627,7 +14627,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14681,7 +14681,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14762,7 +14762,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14789,7 +14789,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14843,7 +14843,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14897,7 +14897,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14924,7 +14924,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14951,7 +14951,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -14978,7 +14978,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15005,7 +15005,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15032,7 +15032,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15059,7 +15059,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15086,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15194,7 +15194,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15221,7 +15221,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15248,7 +15248,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15275,7 +15275,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15356,7 +15356,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15383,7 +15383,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15410,7 +15410,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15437,7 +15437,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15464,7 +15464,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15491,7 +15491,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15518,7 +15518,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15545,7 +15545,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15599,7 +15599,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15626,7 +15626,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15707,7 +15707,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15788,7 +15788,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15815,7 +15815,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15842,7 +15842,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15869,7 +15869,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15896,7 +15896,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15923,7 +15923,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15950,7 +15950,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -15977,7 +15977,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16085,7 +16085,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16112,7 +16112,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16139,7 +16139,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16247,7 +16247,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16301,7 +16301,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16355,7 +16355,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16409,7 +16409,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16463,7 +16463,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16490,7 +16490,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16517,7 +16517,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16544,7 +16544,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16571,7 +16571,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16625,7 +16625,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16679,7 +16679,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16706,7 +16706,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16733,7 +16733,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16760,7 +16760,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16787,7 +16787,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16841,7 +16841,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16868,7 +16868,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16895,7 +16895,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16922,7 +16922,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16949,7 +16949,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17003,7 +17003,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17057,7 +17057,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17084,7 +17084,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17138,7 +17138,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17165,7 +17165,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17192,7 +17192,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17246,7 +17246,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17273,7 +17273,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17300,7 +17300,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17354,7 +17354,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17381,7 +17381,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17408,7 +17408,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17435,7 +17435,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17489,7 +17489,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17516,7 +17516,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17543,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17597,7 +17597,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17624,7 +17624,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17705,7 +17705,7 @@
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17732,7 +17732,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17759,7 +17759,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17786,7 +17786,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17813,7 +17813,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17840,7 +17840,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17867,7 +17867,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17921,7 +17921,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -17975,7 +17975,7 @@
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18002,7 +18002,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18056,7 +18056,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18083,7 +18083,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18110,7 +18110,7 @@
       </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18137,7 +18137,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18164,7 +18164,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18218,7 +18218,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18245,7 +18245,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18272,7 +18272,7 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18299,7 +18299,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18353,7 +18353,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18407,7 +18407,7 @@
       </c>
       <c r="E181" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18434,7 +18434,7 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18461,7 +18461,7 @@
       </c>
       <c r="E183" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18515,7 +18515,7 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18542,7 +18542,7 @@
       </c>
       <c r="E186" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18569,7 +18569,7 @@
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18596,7 +18596,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18623,7 +18623,7 @@
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18657,7 +18657,7 @@
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18684,7 +18684,7 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18738,7 +18738,7 @@
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18792,7 +18792,7 @@
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18819,7 +18819,7 @@
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18846,7 +18846,7 @@
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18873,7 +18873,7 @@
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -18900,7 +18900,7 @@
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19119,7 +19119,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19179,7 +19179,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19213,7 +19213,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19247,7 +19247,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19281,7 +19281,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19308,7 +19308,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19335,7 +19335,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19362,7 +19362,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19470,7 +19470,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19497,7 +19497,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19551,7 +19551,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19578,7 +19578,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19605,7 +19605,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19632,7 +19632,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19659,7 +19659,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19686,7 +19686,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19767,7 +19767,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19794,7 +19794,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19821,7 +19821,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19875,7 +19875,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19902,7 +19902,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19929,7 +19929,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -19983,7 +19983,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20037,7 +20037,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20064,7 +20064,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20145,7 +20145,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20172,7 +20172,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20253,7 +20253,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20280,7 +20280,7 @@
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20307,7 +20307,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20361,7 +20361,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20388,7 +20388,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20415,7 +20415,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20442,7 +20442,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20469,7 +20469,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20523,7 +20523,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20550,7 +20550,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20604,7 +20604,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20631,7 +20631,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20658,7 +20658,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20739,7 +20739,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20766,7 +20766,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20793,7 +20793,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20820,7 +20820,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20874,7 +20874,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20901,7 +20901,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20928,7 +20928,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -20982,7 +20982,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21009,7 +21009,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21036,7 +21036,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21063,7 +21063,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21090,7 +21090,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21117,7 +21117,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21144,7 +21144,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21171,7 +21171,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21252,7 +21252,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21279,7 +21279,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21333,7 +21333,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21360,7 +21360,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21387,7 +21387,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21414,7 +21414,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21441,7 +21441,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21495,7 +21495,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21549,7 +21549,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21576,7 +21576,7 @@
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21603,7 +21603,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21630,7 +21630,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21657,7 +21657,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21711,7 +21711,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21738,7 +21738,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21765,7 +21765,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21792,7 +21792,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21819,7 +21819,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21846,7 +21846,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21873,7 +21873,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21900,7 +21900,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21927,7 +21927,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21954,7 +21954,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -21981,7 +21981,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22008,7 +22008,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22035,7 +22035,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22062,7 +22062,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22089,7 +22089,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22116,7 +22116,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22170,7 +22170,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22197,7 +22197,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22224,7 +22224,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22251,7 +22251,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22359,7 +22359,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22386,7 +22386,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22413,7 +22413,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22440,7 +22440,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22467,7 +22467,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22494,7 +22494,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22521,7 +22521,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22548,7 +22548,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22575,7 +22575,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22602,7 +22602,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22629,7 +22629,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22656,7 +22656,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22683,7 +22683,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22710,7 +22710,7 @@
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22744,7 +22744,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22778,7 +22778,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22805,7 +22805,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22832,7 +22832,7 @@
       </c>
       <c r="E142" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22859,7 +22859,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22947,7 +22947,7 @@
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -22974,7 +22974,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23001,7 +23001,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23028,7 +23028,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23055,7 +23055,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23082,7 +23082,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23116,7 +23116,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23150,7 +23150,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23184,7 +23184,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23218,7 +23218,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23245,7 +23245,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23272,7 +23272,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23306,7 +23306,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23374,7 +23374,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23435,7 +23435,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23496,7 +23496,7 @@
       </c>
       <c r="E174" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23550,7 +23550,7 @@
       </c>
       <c r="E176" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23577,7 +23577,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23604,7 +23604,7 @@
       </c>
       <c r="E178" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23631,7 +23631,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23658,7 +23658,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23692,7 +23692,7 @@
       </c>
       <c r="E182" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23726,7 +23726,7 @@
       </c>
       <c r="E184" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23753,7 +23753,7 @@
       </c>
       <c r="E185" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23787,7 +23787,7 @@
       </c>
       <c r="E187" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23814,7 +23814,7 @@
       </c>
       <c r="E188" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23841,7 +23841,7 @@
       </c>
       <c r="E189" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23868,7 +23868,7 @@
       </c>
       <c r="E190" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23895,7 +23895,7 @@
       </c>
       <c r="E191" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23922,7 +23922,7 @@
       </c>
       <c r="E192" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23949,7 +23949,7 @@
       </c>
       <c r="E193" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -23976,7 +23976,7 @@
       </c>
       <c r="E194" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24003,7 +24003,7 @@
       </c>
       <c r="E195" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24030,7 +24030,7 @@
       </c>
       <c r="E196" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24057,7 +24057,7 @@
       </c>
       <c r="E197" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24084,7 +24084,7 @@
       </c>
       <c r="E198" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24111,7 +24111,7 @@
       </c>
       <c r="E199" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24138,7 +24138,7 @@
       </c>
       <c r="E200" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24165,7 +24165,7 @@
       </c>
       <c r="E201" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24192,7 +24192,7 @@
       </c>
       <c r="E202" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24219,7 +24219,7 @@
       </c>
       <c r="E203" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24246,7 +24246,7 @@
       </c>
       <c r="E204" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24273,7 +24273,7 @@
       </c>
       <c r="E205" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="E206" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24327,7 +24327,7 @@
       </c>
       <c r="E207" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24354,7 +24354,7 @@
       </c>
       <c r="E208" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24381,7 +24381,7 @@
       </c>
       <c r="E209" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24408,7 +24408,7 @@
       </c>
       <c r="E210" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24435,7 +24435,7 @@
       </c>
       <c r="E211" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24462,7 +24462,7 @@
       </c>
       <c r="E212" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24489,7 +24489,7 @@
       </c>
       <c r="E213" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24516,7 +24516,7 @@
       </c>
       <c r="E214" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24543,7 +24543,7 @@
       </c>
       <c r="E215" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24570,7 +24570,7 @@
       </c>
       <c r="E216" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24597,7 +24597,7 @@
       </c>
       <c r="E217" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24624,7 +24624,7 @@
       </c>
       <c r="E218" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24651,7 +24651,7 @@
       </c>
       <c r="E219" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24678,7 +24678,7 @@
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24705,7 +24705,7 @@
       </c>
       <c r="E221" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24732,7 +24732,7 @@
       </c>
       <c r="E222" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24759,7 +24759,7 @@
       </c>
       <c r="E223" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24786,7 +24786,7 @@
       </c>
       <c r="E224" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24813,7 +24813,7 @@
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24840,7 +24840,7 @@
       </c>
       <c r="E226" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24867,7 +24867,7 @@
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24894,7 +24894,7 @@
       </c>
       <c r="E228" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24921,7 +24921,7 @@
       </c>
       <c r="E229" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24948,7 +24948,7 @@
       </c>
       <c r="E230" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
       </c>
       <c r="E232" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="E234" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25043,7 +25043,7 @@
       </c>
       <c r="E235" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25070,7 +25070,7 @@
       </c>
       <c r="E236" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25097,7 +25097,7 @@
       </c>
       <c r="E237" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25336,7 +25336,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25396,7 +25396,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25464,7 +25464,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25491,7 +25491,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25518,7 +25518,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25545,7 +25545,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25572,7 +25572,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25606,7 +25606,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25633,7 +25633,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25660,7 +25660,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25687,7 +25687,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25714,7 +25714,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25741,7 +25741,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25768,7 +25768,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25795,7 +25795,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25834,7 +25834,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25894,7 +25894,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25928,7 +25928,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25955,7 +25955,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -25982,7 +25982,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26009,7 +26009,7 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26036,7 +26036,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26070,7 +26070,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26097,7 +26097,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26165,7 +26165,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26199,7 +26199,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26226,7 +26226,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26260,7 +26260,7 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26321,7 +26321,7 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26348,7 +26348,7 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26375,7 +26375,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26402,7 +26402,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26429,7 +26429,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26456,7 +26456,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26483,7 +26483,7 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26517,7 +26517,7 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26571,7 +26571,7 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26598,7 +26598,7 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26625,7 +26625,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26652,7 +26652,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26679,7 +26679,7 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26706,7 +26706,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26760,7 +26760,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26787,7 +26787,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26821,7 +26821,7 @@
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26848,7 +26848,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26882,7 +26882,7 @@
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26909,7 +26909,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26936,7 +26936,7 @@
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26963,7 +26963,7 @@
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -26990,7 +26990,7 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27017,7 +27017,7 @@
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27044,7 +27044,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27071,7 +27071,7 @@
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27098,7 +27098,7 @@
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27125,7 +27125,7 @@
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27152,7 +27152,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27179,7 +27179,7 @@
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27233,7 +27233,7 @@
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27260,7 +27260,7 @@
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27287,7 +27287,7 @@
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27341,7 +27341,7 @@
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27368,7 +27368,7 @@
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27395,7 +27395,7 @@
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27422,7 +27422,7 @@
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27449,7 +27449,7 @@
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27476,7 +27476,7 @@
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27503,7 +27503,7 @@
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27530,7 +27530,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27557,7 +27557,7 @@
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27584,7 +27584,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27611,7 +27611,7 @@
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27665,7 +27665,7 @@
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27692,7 +27692,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27719,7 +27719,7 @@
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27746,7 +27746,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27773,7 +27773,7 @@
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27800,7 +27800,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27827,7 +27827,7 @@
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27854,7 +27854,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27881,7 +27881,7 @@
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27908,7 +27908,7 @@
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27935,7 +27935,7 @@
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27962,7 +27962,7 @@
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -27989,7 +27989,7 @@
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28016,7 +28016,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28043,7 +28043,7 @@
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28104,7 +28104,7 @@
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28138,7 +28138,7 @@
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28165,7 +28165,7 @@
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28192,7 +28192,7 @@
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28219,7 +28219,7 @@
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28246,7 +28246,7 @@
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28273,7 +28273,7 @@
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28300,7 +28300,7 @@
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28354,7 +28354,7 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28381,7 +28381,7 @@
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28408,7 +28408,7 @@
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28435,7 +28435,7 @@
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28462,7 +28462,7 @@
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28489,7 +28489,7 @@
       </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28516,7 +28516,7 @@
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28543,7 +28543,7 @@
       </c>
       <c r="E110" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28570,7 +28570,7 @@
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28597,7 +28597,7 @@
       </c>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28624,7 +28624,7 @@
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28651,7 +28651,7 @@
       </c>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28678,7 +28678,7 @@
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28705,7 +28705,7 @@
       </c>
       <c r="E116" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28732,7 +28732,7 @@
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28759,7 +28759,7 @@
       </c>
       <c r="E118" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28786,7 +28786,7 @@
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28813,7 +28813,7 @@
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28840,7 +28840,7 @@
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28867,7 +28867,7 @@
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28894,7 +28894,7 @@
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28921,7 +28921,7 @@
       </c>
       <c r="E124" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28948,7 +28948,7 @@
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -28975,7 +28975,7 @@
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29002,7 +29002,7 @@
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29029,7 +29029,7 @@
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29063,7 +29063,7 @@
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29090,7 +29090,7 @@
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29117,7 +29117,7 @@
       </c>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29144,7 +29144,7 @@
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29171,7 +29171,7 @@
       </c>
       <c r="E134" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29198,7 +29198,7 @@
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29232,7 +29232,7 @@
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29259,7 +29259,7 @@
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29286,7 +29286,7 @@
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29313,7 +29313,7 @@
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29340,7 +29340,7 @@
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29374,7 +29374,7 @@
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29401,7 +29401,7 @@
       </c>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29428,7 +29428,7 @@
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29455,7 +29455,7 @@
       </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29489,7 +29489,7 @@
       </c>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29516,7 +29516,7 @@
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29543,7 +29543,7 @@
       </c>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29570,7 +29570,7 @@
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29597,7 +29597,7 @@
       </c>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29624,7 +29624,7 @@
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29651,7 +29651,7 @@
       </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29685,7 +29685,7 @@
       </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29739,7 +29739,7 @@
       </c>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29766,7 +29766,7 @@
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29793,7 +29793,7 @@
       </c>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29820,7 +29820,7 @@
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29847,7 +29847,7 @@
       </c>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29874,7 +29874,7 @@
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29901,7 +29901,7 @@
       </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29935,7 +29935,7 @@
       </c>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29962,7 +29962,7 @@
       </c>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -29989,7 +29989,7 @@
       </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -30016,7 +30016,7 @@
       </c>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -30050,7 +30050,7 @@
       </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -30077,7 +30077,7 @@
       </c>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -30104,7 +30104,7 @@
       </c>
       <c r="E173" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -30138,7 +30138,7 @@
       </c>
       <c r="E175" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -30172,7 +30172,7 @@
       </c>
       <c r="E177" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -30206,7 +30206,7 @@
       </c>
       <c r="E179" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
@@ -30233,7 +30233,7 @@
       </c>
       <c r="E180" s="3" t="inlineStr">
         <is>
-          <t>first copy · last copy · all dates</t>
+          <t>first copy · last copy · latest saved copy</t>
         </is>
       </c>
     </row>
